--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484720_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484720_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6664</v>
+        <v>6.0276</v>
       </c>
       <c r="E2" t="n">
-        <v>6.4449</v>
+        <v>5.568</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2215</v>
+        <v>0.4596</v>
       </c>
       <c r="G2" t="n">
         <v>1.2555</v>
@@ -610,13 +610,13 @@
         <v>1.5096</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2032</v>
+        <v>1.5644</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9763</v>
+        <v>1.0993</v>
       </c>
       <c r="U2" t="n">
-        <v>0.227</v>
+        <v>0.465</v>
       </c>
       <c r="V2" t="n">
         <v>1.8868</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8875</v>
+        <v>1.5385</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0032</v>
+        <v>1.5748</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1157</v>
+        <v>-0.0364</v>
       </c>
       <c r="G3" t="n">
         <v>-0.8983</v>
@@ -688,13 +688,13 @@
         <v>2.8305</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5972</v>
+        <v>0.2482</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0915</v>
+        <v>0.6632</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4943</v>
+        <v>-0.4149</v>
       </c>
       <c r="V3" t="n">
         <v>2.1886</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0461</v>
+        <v>0.0068</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0461</v>
+        <v>0.0068</v>
       </c>
       <c r="G4" t="n">
         <v>0.5682</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.6143</v>
+        <v>-0.5614</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6143</v>
+        <v>-0.5614</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>B. TERREROS RIVAS</t>
+          <t>C. GILABERT FERRI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.0989</v>
+        <v>-2.0283</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.9305</v>
+        <v>-1.7718</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1684</v>
+        <v>-0.2565</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6857</v>
+        <v>-1.9702</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.8353</v>
+        <v>-1.8383</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1496</v>
+        <v>-0.1319</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.7111</v>
+        <v>-0.545</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.4926</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7815</v>
+        <v>0.0411</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0254</v>
+        <v>-1.4252</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3428</v>
+        <v>-1.2521</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3682</v>
+        <v>-0.173</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9435</v>
+        <v>0.1887</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>1.3209</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2093</v>
+        <v>-0.2468</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1205</v>
+        <v>-0.0945</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0888</v>
+        <v>-0.1522</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.566</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-2.1696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. GILABERT FERRI</t>
+          <t>B. TERREROS RIVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1883</v>
+        <v>-2.1627</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.0641</v>
+        <v>-1.6769</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1242</v>
+        <v>-0.4858</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.9702</v>
+        <v>-1.6857</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.8383</v>
+        <v>-2.8353</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1319</v>
+        <v>1.1496</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.545</v>
+        <v>-1.7111</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-2.4926</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0411</v>
+        <v>0.7815</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4252</v>
+        <v>0.0254</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.2521</v>
+        <v>-0.3428</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.173</v>
+        <v>0.3682</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3209</v>
+        <v>1.887</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4068</v>
+        <v>0.1455</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3868</v>
+        <v>0.3741</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.02</v>
+        <v>-0.2286</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.566</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2194</v>
+        <v>-2.3252</v>
       </c>
       <c r="E7" t="n">
         <v>-1.7374</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.482</v>
+        <v>-0.5878</v>
       </c>
       <c r="G7" t="n">
         <v>-3.4153</v>
@@ -1000,13 +1000,13 @@
         <v>2.2644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3656</v>
+        <v>0.2598</v>
       </c>
       <c r="T7" t="n">
         <v>0.2656</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1</v>
+        <v>-0.0058</v>
       </c>
       <c r="V7" t="n">
         <v>0.6415999999999999</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.9499</v>
+        <v>-3.2981</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.1186</v>
+        <v>-3.5727</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1688</v>
+        <v>0.2746</v>
       </c>
       <c r="G8" t="n">
         <v>-0.8613</v>
@@ -1078,13 +1078,13 @@
         <v>1.5096</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1451</v>
+        <v>-0.4933</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7642</v>
+        <v>-0.2183</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3809</v>
+        <v>-0.2751</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6226</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GARCIA NAVEA</t>
+          <t>J. NUNEZ NIEVAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.5153</v>
+        <v>-5.3531</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.0387</v>
+        <v>-4.1654</v>
       </c>
       <c r="F9" t="n">
-        <v>0.5234</v>
+        <v>-1.1876</v>
       </c>
       <c r="G9" t="n">
-        <v>-3.117</v>
+        <v>-2.4296</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.9003</v>
+        <v>-1.2584</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2167</v>
+        <v>-1.1712</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.9927</v>
+        <v>-1.2157</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8014</v>
+        <v>0.0423</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1913</v>
+        <v>-1.258</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1243</v>
+        <v>-1.2139</v>
       </c>
       <c r="N9" t="n">
-        <v>-2.0989</v>
+        <v>-1.3007</v>
       </c>
       <c r="O9" t="n">
-        <v>0.9746</v>
+        <v>0.0868</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.9062</v>
+        <v>-1.887</v>
       </c>
       <c r="Q9" t="n">
-        <v>-7.7367</v>
+        <v>-2.8305</v>
       </c>
       <c r="R9" t="n">
-        <v>2.8305</v>
+        <v>0.9435</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6025</v>
+        <v>-0.7347</v>
       </c>
       <c r="T9" t="n">
-        <v>1.5401</v>
+        <v>-0.1192</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0624</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9054</v>
+        <v>-0.3018</v>
       </c>
       <c r="W9" t="n">
-        <v>2.1506</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. NUNEZ NIEVAS</t>
+          <t>B. ZHENG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.6454</v>
+        <v>-6.1502</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4577</v>
+        <v>-5.9264</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1876</v>
+        <v>-0.2239</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4296</v>
+        <v>-2.4233</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2584</v>
+        <v>-1.2044</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1712</v>
+        <v>-1.2189</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2157</v>
+        <v>-0.7863</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0423</v>
+        <v>-0.1949</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.258</v>
+        <v>-0.5914</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2139</v>
+        <v>-1.637</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3007</v>
+        <v>-1.0095</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0868</v>
+        <v>-0.6274999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.887</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.8305</v>
+        <v>-4.9062</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9435</v>
+        <v>2.8305</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.027</v>
+        <v>-0.4061</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4115</v>
+        <v>-0.2339</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6153999999999999</v>
+        <v>-0.1722</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3018</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. ZHENG</t>
+          <t>J. GARCIA NAVEA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-7.235</v>
+        <v>-6.3056</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.6672</v>
+        <v>-6.5645</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5678</v>
+        <v>0.2589</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.4233</v>
+        <v>-3.117</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2044</v>
+        <v>-2.9003</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2189</v>
+        <v>-0.2167</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.7863</v>
+        <v>-1.9927</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1949</v>
+        <v>-0.8014</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5914</v>
+        <v>-1.1913</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.637</v>
+        <v>-1.1243</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0095</v>
+        <v>-2.0989</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.6274999999999999</v>
+        <v>0.9746</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.0757</v>
+        <v>-4.9062</v>
       </c>
       <c r="Q11" t="n">
-        <v>-4.9062</v>
+        <v>-7.7367</v>
       </c>
       <c r="R11" t="n">
         <v>2.8305</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.4908</v>
+        <v>0.8121</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9747</v>
+        <v>1.0143</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5161</v>
+        <v>-0.2021</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2452</v>
+        <v>0.9054</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.1506</v>
       </c>
       <c r="X11" t="n">
         <v>-1.2452</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-20.3444</v>
+        <v>-20.0503</v>
       </c>
       <c r="E12" t="n">
-        <v>-18.5661</v>
+        <v>-18.2723</v>
       </c>
       <c r="F12" t="n">
         <v>-1.7781</v>
@@ -1378,7 +1378,7 @@
         <v>-11.0658</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6470000000000001</v>
+        <v>-0.6469999999999999</v>
       </c>
       <c r="P12" t="n">
         <v>-7.548</v>
@@ -1390,13 +1390,13 @@
         <v>17.9265</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2938000000000001</v>
+        <v>0.5877</v>
       </c>
       <c r="T12" t="n">
-        <v>2.4568</v>
+        <v>2.750599999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.1628</v>
+        <v>-2.1627</v>
       </c>
       <c r="V12" t="n">
         <v>1.8868</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.2098</v>
+        <v>5.2762</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2444</v>
+        <v>2.9036</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9655</v>
+        <v>2.3726</v>
       </c>
       <c r="G13" t="n">
-        <v>2.1978</v>
+        <v>3.9029</v>
       </c>
       <c r="H13" t="n">
-        <v>3.4403</v>
+        <v>1.8274</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2424</v>
+        <v>2.0755</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0145</v>
+        <v>2.8867</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4996</v>
+        <v>1.5691</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.485</v>
+        <v>1.3176</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1833</v>
+        <v>1.0162</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9407</v>
+        <v>0.2583</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.7574</v>
+        <v>0.7579</v>
       </c>
       <c r="P13" t="n">
-        <v>1.887</v>
+        <v>0.9435</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9435</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
         <v>2.8305</v>
       </c>
       <c r="S13" t="n">
-        <v>1.144</v>
+        <v>0.7316</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8905</v>
+        <v>0.6586</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2534</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.019</v>
+        <v>-0.3018</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2828</v>
+        <v>1.2452</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3018</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>O. TALENS ALBERO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.273</v>
+        <v>4.9708</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3189</v>
+        <v>0.598</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9541</v>
+        <v>4.3728</v>
       </c>
       <c r="G14" t="n">
-        <v>3.9029</v>
+        <v>7.3054</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8274</v>
+        <v>4.8004</v>
       </c>
       <c r="I14" t="n">
-        <v>2.0755</v>
+        <v>2.5049</v>
       </c>
       <c r="J14" t="n">
-        <v>2.8867</v>
+        <v>6.321</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5691</v>
+        <v>3.7298</v>
       </c>
       <c r="L14" t="n">
-        <v>1.3176</v>
+        <v>2.5912</v>
       </c>
       <c r="M14" t="n">
-        <v>1.0162</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2583</v>
+        <v>1.0706</v>
       </c>
       <c r="O14" t="n">
-        <v>0.7579</v>
+        <v>-0.0863</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9435</v>
+        <v>-3.3966</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.887</v>
+        <v>-6.6045</v>
       </c>
       <c r="R14" t="n">
-        <v>2.8305</v>
+        <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2716</v>
+        <v>0.7602</v>
       </c>
       <c r="T14" t="n">
-        <v>0.074</v>
+        <v>0.5797</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3456</v>
+        <v>0.1805</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.3018</v>
+        <v>0.3018</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. AJAYI</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2364</v>
+        <v>4.7263</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0226</v>
+        <v>1.6598</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2138</v>
+        <v>3.0666</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9695</v>
+        <v>2.1978</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3891</v>
+        <v>3.4403</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5803</v>
+        <v>-1.2424</v>
       </c>
       <c r="J15" t="n">
-        <v>0.3522</v>
+        <v>2.0145</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9195</v>
+        <v>2.4996</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5673</v>
+        <v>-0.485</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6172</v>
+        <v>0.1833</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4696</v>
+        <v>0.9407</v>
       </c>
       <c r="O15" t="n">
-        <v>1.1476</v>
+        <v>-0.7574</v>
       </c>
       <c r="P15" t="n">
         <v>1.887</v>
@@ -1624,28 +1624,28 @@
         <v>2.8305</v>
       </c>
       <c r="S15" t="n">
-        <v>0.07820000000000001</v>
+        <v>0.6604</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3121</v>
+        <v>0.3059</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2339</v>
+        <v>0.3545</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3018</v>
+        <v>-0.019</v>
       </c>
       <c r="W15" t="n">
-        <v>0.3018</v>
+        <v>0.2828</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. TALENS ALBERO</t>
+          <t>F. AJAYI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.2142</v>
+        <v>4.2147</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.08400000000000001</v>
+        <v>-0.3671</v>
       </c>
       <c r="F16" t="n">
-        <v>4.2982</v>
+        <v>4.5818</v>
       </c>
       <c r="G16" t="n">
-        <v>7.3054</v>
+        <v>1.9695</v>
       </c>
       <c r="H16" t="n">
-        <v>4.8004</v>
+        <v>1.3891</v>
       </c>
       <c r="I16" t="n">
-        <v>2.5049</v>
+        <v>0.5803</v>
       </c>
       <c r="J16" t="n">
-        <v>6.321</v>
+        <v>0.3522</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7298</v>
+        <v>0.9195</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5912</v>
+        <v>-0.5673</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9844000000000001</v>
+        <v>1.6172</v>
       </c>
       <c r="N16" t="n">
-        <v>1.0706</v>
+        <v>0.4696</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0863</v>
+        <v>1.1476</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.3966</v>
+        <v>1.887</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.6045</v>
+        <v>-0.9435</v>
       </c>
       <c r="R16" t="n">
-        <v>3.2079</v>
+        <v>2.8305</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0036</v>
+        <v>0.0564</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1023</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1059</v>
+        <v>0.1341</v>
       </c>
       <c r="V16" t="n">
         <v>0.3018</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.9001</v>
+        <v>3.7883</v>
       </c>
       <c r="E17" t="n">
-        <v>3.2514</v>
+        <v>2.9591</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6487000000000001</v>
+        <v>0.8292</v>
       </c>
       <c r="G17" t="n">
         <v>3.7722</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8071</v>
+        <v>0.6953</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9587</v>
+        <v>0.6664</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1516</v>
+        <v>0.0289</v>
       </c>
       <c r="V17" t="n">
         <v>-0.3018</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.4636</v>
+        <v>3.1894</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5415</v>
+        <v>1.3466</v>
       </c>
       <c r="F18" t="n">
-        <v>1.9221</v>
+        <v>1.8428</v>
       </c>
       <c r="G18" t="n">
         <v>1.1956</v>
@@ -1858,13 +1858,13 @@
         <v>2.6418</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0529</v>
+        <v>-0.3271</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4173</v>
+        <v>0.2224</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4702</v>
+        <v>-0.5496</v>
       </c>
       <c r="V18" t="n">
         <v>0.6226</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6829</v>
+        <v>1.2583</v>
       </c>
       <c r="E19" t="n">
-        <v>0.328</v>
+        <v>0.0357</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3549</v>
+        <v>1.2226</v>
       </c>
       <c r="G19" t="n">
         <v>-0.6356000000000001</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9976</v>
+        <v>0.573</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.11</v>
+        <v>-0.0223</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ TORRES</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.2828</v>
+        <v>1.2458</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1789</v>
+        <v>-0.518</v>
       </c>
       <c r="F20" t="n">
-        <v>2.4618</v>
+        <v>1.7638</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7744</v>
+        <v>-0.4207</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06419999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="I20" t="n">
-        <v>0.7103</v>
+        <v>-1.3207</v>
       </c>
       <c r="J20" t="n">
-        <v>0.2779</v>
+        <v>-0.4962</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1956</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0823</v>
+        <v>-1.2991</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4965</v>
+        <v>0.0755</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1315</v>
+        <v>0.097</v>
       </c>
       <c r="O20" t="n">
-        <v>0.628</v>
+        <v>-0.0216</v>
       </c>
       <c r="P20" t="n">
-        <v>0.5661</v>
+        <v>2.0757</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.4531</v>
+        <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6613</v>
+        <v>-0.4092</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1735</v>
+        <v>-0.0218</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4879</v>
+        <v>-0.3874</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>J. DOMINGUEZ TORRES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7766999999999999</v>
+        <v>1.1121</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9077</v>
+        <v>-1.3738</v>
       </c>
       <c r="F21" t="n">
-        <v>1.6844</v>
+        <v>2.4859</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4207</v>
+        <v>0.7744</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3207</v>
+        <v>0.7103</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4962</v>
+        <v>0.2779</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.1956</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2991</v>
+        <v>0.0823</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0755</v>
+        <v>0.4965</v>
       </c>
       <c r="N21" t="n">
-        <v>0.097</v>
+        <v>-0.1315</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.0216</v>
+        <v>0.628</v>
       </c>
       <c r="P21" t="n">
-        <v>2.0757</v>
+        <v>0.5661</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0757</v>
+        <v>2.4531</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8783</v>
+        <v>-0.8321</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4115</v>
+        <v>-0.3683</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4667</v>
+        <v>-0.4638</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2852</v>
+        <v>0.5594</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0213</v>
+        <v>0.2161</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2639</v>
+        <v>0.3433</v>
       </c>
       <c r="G22" t="n">
         <v>-0.7279</v>
@@ -2170,13 +2170,13 @@
         <v>0.5661</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1946</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0465</v>
+        <v>0.1484</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1481</v>
+        <v>-0.0688</v>
       </c>
       <c r="V22" t="n">
         <v>0.6415999999999999</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.3922</v>
+        <v>-3.1528</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6394</v>
+        <v>-1.3471</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.7528</v>
+        <v>-1.8057</v>
       </c>
       <c r="G23" t="n">
         <v>-1.923</v>
@@ -2248,13 +2248,13 @@
         <v>1.1322</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4127</v>
+        <v>-0.1733</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4115</v>
+        <v>-0.1192</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0012</v>
+        <v>-0.0541</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2452</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5883</v>
+        <v>-5.545</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.14</v>
+        <v>-4.3348</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4483</v>
+        <v>-1.2102</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4336</v>
@@ -2326,13 +2326,13 @@
         <v>2.0757</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.853</v>
+        <v>-0.8098</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2323</v>
+        <v>-0.4271</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6207</v>
+        <v>-0.3827</v>
       </c>
       <c r="V24" t="n">
         <v>-2.4904</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>20.3442</v>
+        <v>21.6435</v>
       </c>
       <c r="E25" t="n">
-        <v>1.778099999999999</v>
+        <v>1.778099999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>18.5663</v>
+        <v>19.8655</v>
       </c>
       <c r="G25" t="n">
         <v>14.97699999999999</v>
@@ -2404,13 +2404,13 @@
         <v>25.4745</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.2939000000000001</v>
+        <v>1.0051</v>
       </c>
       <c r="T25" t="n">
-        <v>2.162599999999999</v>
+        <v>2.1626</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.4566</v>
+        <v>-1.1578</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8868</v>
